--- a/haustec_202605.xlsx
+++ b/haustec_202605.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8497A3D-9FA1-4F11-AF3F-6B7B098E7A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6779DED-A374-4A32-807E-FF00C527B049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -122,19 +122,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,7 +459,7 @@
       <c r="B2" s="2">
         <v>46143</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>46136</v>
       </c>
     </row>
@@ -473,7 +470,7 @@
       <c r="B3" s="2">
         <v>46149</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>46139</v>
       </c>
     </row>
@@ -484,7 +481,7 @@
       <c r="B4" s="2">
         <v>46153</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>46149</v>
       </c>
     </row>
@@ -495,7 +492,7 @@
       <c r="B5" s="2">
         <v>46155</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>46153</v>
       </c>
     </row>
@@ -506,7 +503,7 @@
       <c r="B6" s="2">
         <v>46157</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>46155</v>
       </c>
     </row>
@@ -517,7 +514,7 @@
       <c r="B7" s="2">
         <v>46161</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -528,7 +525,7 @@
       <c r="B8" s="2">
         <v>46163</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>46161</v>
       </c>
     </row>
@@ -539,7 +536,7 @@
       <c r="B9" s="2">
         <v>46164</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>46162</v>
       </c>
     </row>
@@ -550,7 +547,7 @@
       <c r="B10" s="2">
         <v>46168</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>46164</v>
       </c>
     </row>
